--- a/prowler-report-template.xlsx
+++ b/prowler-report-template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\micvirgi\Documents\Code Repo\GitHub\multi-account-security-assessment-via-prowler\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89C2208E-6F39-41EB-9D2B-5C6BBEE5BE33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{09368247-AD61-4422-BDE2-017266CBE771}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="26928" yWindow="-8700" windowWidth="33600" windowHeight="20496" xr2:uid="{0487832F-E362-F645-8976-2EFD8C4D20FE}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{0487832F-E362-F645-8976-2EFD8C4D20FE}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="11" r:id="rId1"/>
@@ -1374,9 +1374,6 @@
     <t>Log Group /aws/lambda/IamPasswordPolicy has less than 365 days retention period (90 days).</t>
   </si>
   <si>
-    <t>This template supports the output of Prowler 4.x.x.  Processing Prowler 3.x or 2.x output will have unexpected results.</t>
-  </si>
-  <si>
     <t>123456789012-Development</t>
   </si>
   <si>
@@ -1927,6 +1924,9 @@
   </si>
   <si>
     <t>Always start with a fesh template. Do not re-use a template with previous customer data. Pivot Tables keep a history of the deleted data source.</t>
+  </si>
+  <si>
+    <t>This template supports the output of Prowler 5.x.x. and 4.x.x.  Processing Prowler 3.x or 2.x output will have unexpected results.</t>
   </si>
 </sst>
 </file>
@@ -13975,7 +13975,7 @@
     </row>
     <row r="2" spans="1:1" s="8" customFormat="1" ht="18.75">
       <c r="A2" s="9" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="3" spans="1:1" s="8" customFormat="1" ht="18.75">
@@ -13990,7 +13990,7 @@
     </row>
     <row r="5" spans="1:1" s="8" customFormat="1" ht="18.75">
       <c r="A5" s="10" t="s">
-        <v>343</v>
+        <v>527</v>
       </c>
     </row>
     <row r="6" spans="1:1" s="8" customFormat="1">
@@ -14028,7 +14028,7 @@
     </row>
     <row r="16" spans="1:1" ht="18.75">
       <c r="A16" s="14" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="17" spans="1:1">
@@ -14323,19 +14323,19 @@
         <v>123456789012</v>
       </c>
       <c r="D2" t="s">
+        <v>343</v>
+      </c>
+      <c r="E2" t="s">
+        <v>521</v>
+      </c>
+      <c r="F2" t="s">
+        <v>523</v>
+      </c>
+      <c r="G2" t="s">
+        <v>524</v>
+      </c>
+      <c r="I2" t="s">
         <v>344</v>
-      </c>
-      <c r="E2" t="s">
-        <v>522</v>
-      </c>
-      <c r="F2" t="s">
-        <v>524</v>
-      </c>
-      <c r="G2" t="s">
-        <v>525</v>
-      </c>
-      <c r="I2" t="s">
-        <v>345</v>
       </c>
       <c r="J2" t="s">
         <v>42</v>
@@ -14353,7 +14353,7 @@
         <v>54</v>
       </c>
       <c r="O2" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="P2" t="b">
         <v>0</v>
@@ -14368,7 +14368,7 @@
         <v>48</v>
       </c>
       <c r="U2" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="V2">
         <v>123456789012</v>
@@ -14415,19 +14415,19 @@
         <v>123456789012</v>
       </c>
       <c r="D3" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F3" t="s">
+        <v>523</v>
+      </c>
+      <c r="G3" t="s">
         <v>524</v>
       </c>
-      <c r="G3" t="s">
-        <v>525</v>
-      </c>
       <c r="I3" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="J3" t="s">
         <v>42</v>
@@ -14445,7 +14445,7 @@
         <v>54</v>
       </c>
       <c r="O3" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="P3" t="b">
         <v>0</v>
@@ -14460,7 +14460,7 @@
         <v>48</v>
       </c>
       <c r="U3" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="V3">
         <v>123456789012</v>
@@ -14507,19 +14507,19 @@
         <v>123456789012</v>
       </c>
       <c r="D4" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E4" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F4" t="s">
+        <v>523</v>
+      </c>
+      <c r="G4" t="s">
         <v>524</v>
       </c>
-      <c r="G4" t="s">
-        <v>525</v>
-      </c>
       <c r="I4" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="J4" t="s">
         <v>42</v>
@@ -14537,7 +14537,7 @@
         <v>54</v>
       </c>
       <c r="O4" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="P4" t="b">
         <v>0</v>
@@ -14552,7 +14552,7 @@
         <v>48</v>
       </c>
       <c r="U4" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="V4">
         <v>123456789012</v>
@@ -14599,19 +14599,19 @@
         <v>123456789012</v>
       </c>
       <c r="D5" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E5" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F5" t="s">
+        <v>523</v>
+      </c>
+      <c r="G5" t="s">
         <v>524</v>
       </c>
-      <c r="G5" t="s">
-        <v>525</v>
-      </c>
       <c r="I5" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="J5" t="s">
         <v>42</v>
@@ -14629,7 +14629,7 @@
         <v>54</v>
       </c>
       <c r="O5" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="P5" t="b">
         <v>0</v>
@@ -14644,7 +14644,7 @@
         <v>48</v>
       </c>
       <c r="U5" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="V5">
         <v>123456789012</v>
@@ -14691,19 +14691,19 @@
         <v>123456789012</v>
       </c>
       <c r="D6" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E6" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F6" t="s">
+        <v>523</v>
+      </c>
+      <c r="G6" t="s">
         <v>524</v>
       </c>
-      <c r="G6" t="s">
-        <v>525</v>
-      </c>
       <c r="I6" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="J6" t="s">
         <v>42</v>
@@ -14721,7 +14721,7 @@
         <v>54</v>
       </c>
       <c r="O6" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="P6" t="b">
         <v>0</v>
@@ -14736,7 +14736,7 @@
         <v>48</v>
       </c>
       <c r="U6" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="V6">
         <v>123456789012</v>
@@ -14783,19 +14783,19 @@
         <v>123456789012</v>
       </c>
       <c r="D7" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E7" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F7" t="s">
+        <v>523</v>
+      </c>
+      <c r="G7" t="s">
         <v>524</v>
       </c>
-      <c r="G7" t="s">
-        <v>525</v>
-      </c>
       <c r="I7" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="J7" t="s">
         <v>42</v>
@@ -14813,7 +14813,7 @@
         <v>54</v>
       </c>
       <c r="O7" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="P7" t="b">
         <v>0</v>
@@ -14828,7 +14828,7 @@
         <v>48</v>
       </c>
       <c r="U7" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="V7">
         <v>123456789012</v>
@@ -14875,19 +14875,19 @@
         <v>123456789012</v>
       </c>
       <c r="D8" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E8" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F8" t="s">
+        <v>523</v>
+      </c>
+      <c r="G8" t="s">
         <v>524</v>
       </c>
-      <c r="G8" t="s">
-        <v>525</v>
-      </c>
       <c r="I8" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="J8" t="s">
         <v>42</v>
@@ -14905,7 +14905,7 @@
         <v>54</v>
       </c>
       <c r="O8" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="P8" t="b">
         <v>0</v>
@@ -14920,7 +14920,7 @@
         <v>48</v>
       </c>
       <c r="U8" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="V8">
         <v>123456789012</v>
@@ -14967,19 +14967,19 @@
         <v>123456789012</v>
       </c>
       <c r="D9" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E9" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F9" t="s">
+        <v>523</v>
+      </c>
+      <c r="G9" t="s">
         <v>524</v>
       </c>
-      <c r="G9" t="s">
-        <v>525</v>
-      </c>
       <c r="I9" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="J9" t="s">
         <v>42</v>
@@ -14997,7 +14997,7 @@
         <v>54</v>
       </c>
       <c r="O9" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="P9" t="b">
         <v>0</v>
@@ -15012,7 +15012,7 @@
         <v>48</v>
       </c>
       <c r="U9" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="V9">
         <v>123456789012</v>
@@ -15059,19 +15059,19 @@
         <v>123456789012</v>
       </c>
       <c r="D10" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E10" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F10" t="s">
+        <v>523</v>
+      </c>
+      <c r="G10" t="s">
         <v>524</v>
       </c>
-      <c r="G10" t="s">
-        <v>525</v>
-      </c>
       <c r="I10" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="J10" t="s">
         <v>42</v>
@@ -15089,7 +15089,7 @@
         <v>54</v>
       </c>
       <c r="O10" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="P10" t="b">
         <v>0</v>
@@ -15104,7 +15104,7 @@
         <v>48</v>
       </c>
       <c r="U10" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="V10">
         <v>123456789012</v>
@@ -15151,19 +15151,19 @@
         <v>123456789012</v>
       </c>
       <c r="D11" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E11" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F11" t="s">
+        <v>523</v>
+      </c>
+      <c r="G11" t="s">
         <v>524</v>
       </c>
-      <c r="G11" t="s">
-        <v>525</v>
-      </c>
       <c r="I11" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="J11" t="s">
         <v>42</v>
@@ -15181,7 +15181,7 @@
         <v>54</v>
       </c>
       <c r="O11" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="P11" t="b">
         <v>0</v>
@@ -15196,7 +15196,7 @@
         <v>48</v>
       </c>
       <c r="U11" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="V11">
         <v>123456789012</v>
@@ -15243,19 +15243,19 @@
         <v>123456789012</v>
       </c>
       <c r="D12" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E12" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F12" t="s">
+        <v>523</v>
+      </c>
+      <c r="G12" t="s">
         <v>524</v>
       </c>
-      <c r="G12" t="s">
-        <v>525</v>
-      </c>
       <c r="I12" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="J12" t="s">
         <v>42</v>
@@ -15273,7 +15273,7 @@
         <v>54</v>
       </c>
       <c r="O12" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="P12" t="b">
         <v>0</v>
@@ -15288,7 +15288,7 @@
         <v>48</v>
       </c>
       <c r="U12" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="V12">
         <v>123456789012</v>
@@ -15335,19 +15335,19 @@
         <v>123456789012</v>
       </c>
       <c r="D13" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E13" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F13" t="s">
+        <v>523</v>
+      </c>
+      <c r="G13" t="s">
         <v>524</v>
       </c>
-      <c r="G13" t="s">
-        <v>525</v>
-      </c>
       <c r="I13" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="J13" t="s">
         <v>42</v>
@@ -15365,7 +15365,7 @@
         <v>54</v>
       </c>
       <c r="O13" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="P13" t="b">
         <v>0</v>
@@ -15380,7 +15380,7 @@
         <v>48</v>
       </c>
       <c r="U13" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="V13">
         <v>123456789012</v>
@@ -15427,19 +15427,19 @@
         <v>123456789012</v>
       </c>
       <c r="D14" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E14" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F14" t="s">
+        <v>523</v>
+      </c>
+      <c r="G14" t="s">
         <v>524</v>
       </c>
-      <c r="G14" t="s">
-        <v>525</v>
-      </c>
       <c r="I14" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="J14" t="s">
         <v>42</v>
@@ -15457,7 +15457,7 @@
         <v>54</v>
       </c>
       <c r="O14" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="P14" t="b">
         <v>0</v>
@@ -15472,7 +15472,7 @@
         <v>48</v>
       </c>
       <c r="U14" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="V14">
         <v>123456789012</v>
@@ -15519,19 +15519,19 @@
         <v>123456789012</v>
       </c>
       <c r="D15" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E15" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F15" t="s">
+        <v>523</v>
+      </c>
+      <c r="G15" t="s">
         <v>524</v>
       </c>
-      <c r="G15" t="s">
-        <v>525</v>
-      </c>
       <c r="I15" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="J15" t="s">
         <v>42</v>
@@ -15549,7 +15549,7 @@
         <v>54</v>
       </c>
       <c r="O15" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="P15" t="b">
         <v>0</v>
@@ -15564,7 +15564,7 @@
         <v>48</v>
       </c>
       <c r="U15" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="V15">
         <v>123456789012</v>
@@ -15611,19 +15611,19 @@
         <v>123456789012</v>
       </c>
       <c r="D16" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E16" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F16" t="s">
+        <v>523</v>
+      </c>
+      <c r="G16" t="s">
         <v>524</v>
       </c>
-      <c r="G16" t="s">
-        <v>525</v>
-      </c>
       <c r="I16" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="J16" t="s">
         <v>42</v>
@@ -15641,7 +15641,7 @@
         <v>54</v>
       </c>
       <c r="O16" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="P16" t="b">
         <v>0</v>
@@ -15656,7 +15656,7 @@
         <v>48</v>
       </c>
       <c r="U16" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="V16">
         <v>123456789012</v>
@@ -15703,19 +15703,19 @@
         <v>123456789012</v>
       </c>
       <c r="D17" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E17" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F17" t="s">
+        <v>523</v>
+      </c>
+      <c r="G17" t="s">
         <v>524</v>
       </c>
-      <c r="G17" t="s">
-        <v>525</v>
-      </c>
       <c r="I17" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="J17" t="s">
         <v>42</v>
@@ -15733,7 +15733,7 @@
         <v>54</v>
       </c>
       <c r="O17" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="P17" t="b">
         <v>0</v>
@@ -15748,7 +15748,7 @@
         <v>48</v>
       </c>
       <c r="U17" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="V17">
         <v>123456789012</v>
@@ -15795,19 +15795,19 @@
         <v>123456789012</v>
       </c>
       <c r="D18" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E18" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F18" t="s">
+        <v>523</v>
+      </c>
+      <c r="G18" t="s">
         <v>524</v>
       </c>
-      <c r="G18" t="s">
-        <v>525</v>
-      </c>
       <c r="I18" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="J18" t="s">
         <v>42</v>
@@ -15825,7 +15825,7 @@
         <v>54</v>
       </c>
       <c r="O18" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="P18" t="b">
         <v>0</v>
@@ -15840,7 +15840,7 @@
         <v>48</v>
       </c>
       <c r="U18" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="V18">
         <v>123456789012</v>
@@ -15887,19 +15887,19 @@
         <v>123456789012</v>
       </c>
       <c r="D19" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E19" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F19" t="s">
+        <v>523</v>
+      </c>
+      <c r="G19" t="s">
         <v>524</v>
       </c>
-      <c r="G19" t="s">
-        <v>525</v>
-      </c>
       <c r="I19" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="J19" t="s">
         <v>42</v>
@@ -15932,7 +15932,7 @@
         <v>48</v>
       </c>
       <c r="U19" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="V19">
         <v>123456789012</v>
@@ -15976,19 +15976,19 @@
         <v>123456789012</v>
       </c>
       <c r="D20" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E20" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F20" t="s">
+        <v>523</v>
+      </c>
+      <c r="G20" t="s">
         <v>524</v>
       </c>
-      <c r="G20" t="s">
-        <v>525</v>
-      </c>
       <c r="I20" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="J20" t="s">
         <v>42</v>
@@ -16018,13 +16018,13 @@
         <v>70</v>
       </c>
       <c r="U20" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="V20" t="s">
         <v>210</v>
       </c>
       <c r="X20" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="Y20" t="s">
         <v>42</v>
@@ -16068,19 +16068,19 @@
         <v>123456789012</v>
       </c>
       <c r="D21" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E21" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F21" t="s">
+        <v>523</v>
+      </c>
+      <c r="G21" t="s">
         <v>524</v>
       </c>
-      <c r="G21" t="s">
-        <v>525</v>
-      </c>
       <c r="I21" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="J21" t="s">
         <v>42</v>
@@ -16110,13 +16110,13 @@
         <v>70</v>
       </c>
       <c r="U21" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="V21" t="s">
         <v>213</v>
       </c>
       <c r="X21" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="Y21" t="s">
         <v>42</v>
@@ -16160,19 +16160,19 @@
         <v>123456789012</v>
       </c>
       <c r="D22" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E22" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F22" t="s">
+        <v>523</v>
+      </c>
+      <c r="G22" t="s">
         <v>524</v>
       </c>
-      <c r="G22" t="s">
-        <v>525</v>
-      </c>
       <c r="I22" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="J22" t="s">
         <v>42</v>
@@ -16202,13 +16202,13 @@
         <v>70</v>
       </c>
       <c r="U22" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="V22" t="s">
         <v>215</v>
       </c>
       <c r="X22" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="Y22" t="s">
         <v>42</v>
@@ -16252,19 +16252,19 @@
         <v>123456789012</v>
       </c>
       <c r="D23" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E23" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F23" t="s">
+        <v>523</v>
+      </c>
+      <c r="G23" t="s">
         <v>524</v>
       </c>
-      <c r="G23" t="s">
-        <v>525</v>
-      </c>
       <c r="I23" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="J23" t="s">
         <v>42</v>
@@ -16294,13 +16294,13 @@
         <v>70</v>
       </c>
       <c r="U23" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="V23" t="s">
         <v>217</v>
       </c>
       <c r="X23" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="Y23" t="s">
         <v>42</v>
@@ -16344,19 +16344,19 @@
         <v>123456789012</v>
       </c>
       <c r="D24" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E24" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F24" t="s">
+        <v>523</v>
+      </c>
+      <c r="G24" t="s">
         <v>524</v>
       </c>
-      <c r="G24" t="s">
-        <v>525</v>
-      </c>
       <c r="I24" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="J24" t="s">
         <v>42</v>
@@ -16386,13 +16386,13 @@
         <v>70</v>
       </c>
       <c r="U24" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="V24" t="s">
         <v>219</v>
       </c>
       <c r="X24" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="Y24" t="s">
         <v>42</v>
@@ -16436,19 +16436,19 @@
         <v>123456789012</v>
       </c>
       <c r="D25" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E25" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F25" t="s">
+        <v>523</v>
+      </c>
+      <c r="G25" t="s">
         <v>524</v>
       </c>
-      <c r="G25" t="s">
-        <v>525</v>
-      </c>
       <c r="I25" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="J25" t="s">
         <v>42</v>
@@ -16478,13 +16478,13 @@
         <v>70</v>
       </c>
       <c r="U25" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="V25" t="s">
         <v>221</v>
       </c>
       <c r="X25" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="Y25" t="s">
         <v>42</v>
@@ -16528,19 +16528,19 @@
         <v>123456789012</v>
       </c>
       <c r="D26" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E26" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F26" t="s">
+        <v>523</v>
+      </c>
+      <c r="G26" t="s">
         <v>524</v>
       </c>
-      <c r="G26" t="s">
-        <v>525</v>
-      </c>
       <c r="I26" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="J26" t="s">
         <v>42</v>
@@ -16570,13 +16570,13 @@
         <v>70</v>
       </c>
       <c r="U26" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="V26" t="s">
         <v>223</v>
       </c>
       <c r="X26" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="Y26" t="s">
         <v>42</v>
@@ -16620,19 +16620,19 @@
         <v>123456789012</v>
       </c>
       <c r="D27" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E27" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F27" t="s">
+        <v>523</v>
+      </c>
+      <c r="G27" t="s">
         <v>524</v>
       </c>
-      <c r="G27" t="s">
-        <v>525</v>
-      </c>
       <c r="I27" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="J27" t="s">
         <v>42</v>
@@ -16662,13 +16662,13 @@
         <v>70</v>
       </c>
       <c r="U27" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="V27" t="s">
         <v>225</v>
       </c>
       <c r="X27" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="Y27" t="s">
         <v>42</v>
@@ -16712,19 +16712,19 @@
         <v>123456789012</v>
       </c>
       <c r="D28" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E28" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F28" t="s">
+        <v>523</v>
+      </c>
+      <c r="G28" t="s">
         <v>524</v>
       </c>
-      <c r="G28" t="s">
-        <v>525</v>
-      </c>
       <c r="I28" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="J28" t="s">
         <v>42</v>
@@ -16754,13 +16754,13 @@
         <v>70</v>
       </c>
       <c r="U28" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="V28" t="s">
         <v>210</v>
       </c>
       <c r="X28" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="Y28" t="s">
         <v>42</v>
@@ -16804,19 +16804,19 @@
         <v>123456789012</v>
       </c>
       <c r="D29" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E29" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F29" t="s">
+        <v>523</v>
+      </c>
+      <c r="G29" t="s">
         <v>524</v>
       </c>
-      <c r="G29" t="s">
-        <v>525</v>
-      </c>
       <c r="I29" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="J29" t="s">
         <v>42</v>
@@ -16846,13 +16846,13 @@
         <v>70</v>
       </c>
       <c r="U29" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="V29" t="s">
         <v>225</v>
       </c>
       <c r="X29" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="Y29" t="s">
         <v>42</v>
@@ -16896,19 +16896,19 @@
         <v>123456789012</v>
       </c>
       <c r="D30" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E30" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F30" t="s">
+        <v>523</v>
+      </c>
+      <c r="G30" t="s">
         <v>524</v>
       </c>
-      <c r="G30" t="s">
-        <v>525</v>
-      </c>
       <c r="I30" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="J30" t="s">
         <v>42</v>
@@ -16938,13 +16938,13 @@
         <v>70</v>
       </c>
       <c r="U30" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="V30" t="s">
         <v>225</v>
       </c>
       <c r="X30" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Y30" t="s">
         <v>42</v>
@@ -16988,19 +16988,19 @@
         <v>123456789012</v>
       </c>
       <c r="D31" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E31" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F31" t="s">
+        <v>523</v>
+      </c>
+      <c r="G31" t="s">
         <v>524</v>
       </c>
-      <c r="G31" t="s">
-        <v>525</v>
-      </c>
       <c r="I31" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="J31" t="s">
         <v>42</v>
@@ -17030,13 +17030,13 @@
         <v>70</v>
       </c>
       <c r="U31" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="V31" t="s">
         <v>217</v>
       </c>
       <c r="X31" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="Y31" t="s">
         <v>42</v>
@@ -17089,19 +17089,19 @@
         <v>123456789012</v>
       </c>
       <c r="D32" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E32" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F32" t="s">
+        <v>523</v>
+      </c>
+      <c r="G32" t="s">
         <v>524</v>
       </c>
-      <c r="G32" t="s">
-        <v>525</v>
-      </c>
       <c r="I32" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="J32" t="s">
         <v>42</v>
@@ -17131,13 +17131,13 @@
         <v>70</v>
       </c>
       <c r="U32" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="V32" t="s">
         <v>225</v>
       </c>
       <c r="X32" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="Y32" t="s">
         <v>42</v>
@@ -17190,19 +17190,19 @@
         <v>123456789012</v>
       </c>
       <c r="D33" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E33" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F33" t="s">
+        <v>523</v>
+      </c>
+      <c r="G33" t="s">
         <v>524</v>
       </c>
-      <c r="G33" t="s">
-        <v>525</v>
-      </c>
       <c r="I33" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="J33" t="s">
         <v>42</v>
@@ -17232,13 +17232,13 @@
         <v>70</v>
       </c>
       <c r="U33" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="V33" t="s">
         <v>225</v>
       </c>
       <c r="X33" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="Y33" t="s">
         <v>42</v>
@@ -17291,19 +17291,19 @@
         <v>123456789012</v>
       </c>
       <c r="D34" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E34" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F34" t="s">
+        <v>523</v>
+      </c>
+      <c r="G34" t="s">
         <v>524</v>
       </c>
-      <c r="G34" t="s">
-        <v>525</v>
-      </c>
       <c r="I34" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="J34" t="s">
         <v>42</v>
@@ -17333,13 +17333,13 @@
         <v>70</v>
       </c>
       <c r="U34" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="V34" t="s">
         <v>225</v>
       </c>
       <c r="X34" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Y34" t="s">
         <v>42</v>
@@ -17392,19 +17392,19 @@
         <v>123456789012</v>
       </c>
       <c r="D35" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E35" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F35" t="s">
+        <v>523</v>
+      </c>
+      <c r="G35" t="s">
         <v>524</v>
       </c>
-      <c r="G35" t="s">
-        <v>525</v>
-      </c>
       <c r="I35" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="J35" t="s">
         <v>42</v>
@@ -17434,7 +17434,7 @@
         <v>88</v>
       </c>
       <c r="U35" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="V35" t="s">
         <v>230</v>
@@ -17487,19 +17487,19 @@
         <v>123456789012</v>
       </c>
       <c r="D36" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E36" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F36" t="s">
+        <v>523</v>
+      </c>
+      <c r="G36" t="s">
         <v>524</v>
       </c>
-      <c r="G36" t="s">
-        <v>525</v>
-      </c>
       <c r="I36" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="J36" t="s">
         <v>42</v>
@@ -17529,7 +17529,7 @@
         <v>88</v>
       </c>
       <c r="U36" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="V36" t="s">
         <v>232</v>
@@ -17582,19 +17582,19 @@
         <v>123456789012</v>
       </c>
       <c r="D37" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E37" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F37" t="s">
+        <v>523</v>
+      </c>
+      <c r="G37" t="s">
         <v>524</v>
       </c>
-      <c r="G37" t="s">
-        <v>525</v>
-      </c>
       <c r="I37" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="J37" t="s">
         <v>42</v>
@@ -17624,7 +17624,7 @@
         <v>88</v>
       </c>
       <c r="U37" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="V37" t="s">
         <v>234</v>
@@ -17677,19 +17677,19 @@
         <v>123456789012</v>
       </c>
       <c r="D38" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E38" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F38" t="s">
+        <v>523</v>
+      </c>
+      <c r="G38" t="s">
         <v>524</v>
       </c>
-      <c r="G38" t="s">
-        <v>525</v>
-      </c>
       <c r="I38" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="J38" t="s">
         <v>42</v>
@@ -17719,7 +17719,7 @@
         <v>88</v>
       </c>
       <c r="U38" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="V38" t="s">
         <v>236</v>
@@ -17772,19 +17772,19 @@
         <v>123456789012</v>
       </c>
       <c r="D39" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E39" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F39" t="s">
+        <v>523</v>
+      </c>
+      <c r="G39" t="s">
         <v>524</v>
       </c>
-      <c r="G39" t="s">
-        <v>525</v>
-      </c>
       <c r="I39" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="J39" t="s">
         <v>42</v>
@@ -17814,7 +17814,7 @@
         <v>88</v>
       </c>
       <c r="U39" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="V39" t="s">
         <v>230</v>
@@ -17864,19 +17864,19 @@
         <v>123456789012</v>
       </c>
       <c r="D40" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E40" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F40" t="s">
+        <v>523</v>
+      </c>
+      <c r="G40" t="s">
         <v>524</v>
       </c>
-      <c r="G40" t="s">
-        <v>525</v>
-      </c>
       <c r="I40" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="J40" t="s">
         <v>42</v>
@@ -17906,7 +17906,7 @@
         <v>88</v>
       </c>
       <c r="U40" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="V40" t="s">
         <v>240</v>
@@ -17956,19 +17956,19 @@
         <v>123456789012</v>
       </c>
       <c r="D41" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E41" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F41" t="s">
+        <v>523</v>
+      </c>
+      <c r="G41" t="s">
         <v>524</v>
       </c>
-      <c r="G41" t="s">
-        <v>525</v>
-      </c>
       <c r="I41" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="J41" t="s">
         <v>42</v>
@@ -17998,7 +17998,7 @@
         <v>88</v>
       </c>
       <c r="U41" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="V41" t="s">
         <v>242</v>
@@ -18048,19 +18048,19 @@
         <v>123456789012</v>
       </c>
       <c r="D42" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E42" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F42" t="s">
+        <v>523</v>
+      </c>
+      <c r="G42" t="s">
         <v>524</v>
       </c>
-      <c r="G42" t="s">
-        <v>525</v>
-      </c>
       <c r="I42" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="J42" t="s">
         <v>42</v>
@@ -18090,7 +18090,7 @@
         <v>88</v>
       </c>
       <c r="U42" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="V42" t="s">
         <v>244</v>
@@ -18140,19 +18140,19 @@
         <v>123456789012</v>
       </c>
       <c r="D43" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E43" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F43" t="s">
+        <v>523</v>
+      </c>
+      <c r="G43" t="s">
         <v>524</v>
       </c>
-      <c r="G43" t="s">
-        <v>525</v>
-      </c>
       <c r="I43" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="J43" t="s">
         <v>42</v>
@@ -18182,7 +18182,7 @@
         <v>88</v>
       </c>
       <c r="U43" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="V43" t="s">
         <v>246</v>
@@ -18232,19 +18232,19 @@
         <v>123456789012</v>
       </c>
       <c r="D44" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E44" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F44" t="s">
+        <v>523</v>
+      </c>
+      <c r="G44" t="s">
         <v>524</v>
       </c>
-      <c r="G44" t="s">
-        <v>525</v>
-      </c>
       <c r="I44" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J44" t="s">
         <v>42</v>
@@ -18274,7 +18274,7 @@
         <v>88</v>
       </c>
       <c r="U44" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="V44" t="s">
         <v>248</v>
@@ -18324,19 +18324,19 @@
         <v>123456789012</v>
       </c>
       <c r="D45" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E45" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F45" t="s">
+        <v>523</v>
+      </c>
+      <c r="G45" t="s">
         <v>524</v>
       </c>
-      <c r="G45" t="s">
-        <v>525</v>
-      </c>
       <c r="I45" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="J45" t="s">
         <v>42</v>
@@ -18366,7 +18366,7 @@
         <v>88</v>
       </c>
       <c r="U45" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="V45" t="s">
         <v>250</v>
@@ -18416,19 +18416,19 @@
         <v>123456789012</v>
       </c>
       <c r="D46" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E46" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F46" t="s">
+        <v>523</v>
+      </c>
+      <c r="G46" t="s">
         <v>524</v>
       </c>
-      <c r="G46" t="s">
-        <v>525</v>
-      </c>
       <c r="I46" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="J46" t="s">
         <v>42</v>
@@ -18458,7 +18458,7 @@
         <v>88</v>
       </c>
       <c r="U46" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="V46" t="s">
         <v>252</v>
@@ -18508,19 +18508,19 @@
         <v>123456789012</v>
       </c>
       <c r="D47" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E47" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F47" t="s">
+        <v>523</v>
+      </c>
+      <c r="G47" t="s">
         <v>524</v>
       </c>
-      <c r="G47" t="s">
-        <v>525</v>
-      </c>
       <c r="I47" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="J47" t="s">
         <v>42</v>
@@ -18550,7 +18550,7 @@
         <v>88</v>
       </c>
       <c r="U47" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="V47" t="s">
         <v>254</v>
@@ -18600,19 +18600,19 @@
         <v>123456789012</v>
       </c>
       <c r="D48" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E48" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F48" t="s">
+        <v>523</v>
+      </c>
+      <c r="G48" t="s">
         <v>524</v>
       </c>
-      <c r="G48" t="s">
-        <v>525</v>
-      </c>
       <c r="I48" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="J48" t="s">
         <v>42</v>
@@ -18642,7 +18642,7 @@
         <v>88</v>
       </c>
       <c r="U48" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="V48" t="s">
         <v>256</v>
@@ -18692,19 +18692,19 @@
         <v>123456789012</v>
       </c>
       <c r="D49" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E49" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F49" t="s">
+        <v>523</v>
+      </c>
+      <c r="G49" t="s">
         <v>524</v>
       </c>
-      <c r="G49" t="s">
-        <v>525</v>
-      </c>
       <c r="I49" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="J49" t="s">
         <v>42</v>
@@ -18734,7 +18734,7 @@
         <v>88</v>
       </c>
       <c r="U49" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="V49" t="s">
         <v>258</v>
@@ -18784,19 +18784,19 @@
         <v>123456789012</v>
       </c>
       <c r="D50" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E50" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F50" t="s">
+        <v>523</v>
+      </c>
+      <c r="G50" t="s">
         <v>524</v>
       </c>
-      <c r="G50" t="s">
-        <v>525</v>
-      </c>
       <c r="I50" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="J50" t="s">
         <v>42</v>
@@ -18826,7 +18826,7 @@
         <v>88</v>
       </c>
       <c r="U50" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="V50" t="s">
         <v>260</v>
@@ -18876,19 +18876,19 @@
         <v>123456789012</v>
       </c>
       <c r="D51" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E51" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F51" t="s">
+        <v>523</v>
+      </c>
+      <c r="G51" t="s">
         <v>524</v>
       </c>
-      <c r="G51" t="s">
-        <v>525</v>
-      </c>
       <c r="I51" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="J51" t="s">
         <v>42</v>
@@ -18918,7 +18918,7 @@
         <v>88</v>
       </c>
       <c r="U51" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="V51" t="s">
         <v>262</v>
@@ -18968,19 +18968,19 @@
         <v>123456789012</v>
       </c>
       <c r="D52" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E52" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F52" t="s">
+        <v>523</v>
+      </c>
+      <c r="G52" t="s">
         <v>524</v>
       </c>
-      <c r="G52" t="s">
-        <v>525</v>
-      </c>
       <c r="I52" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="J52" t="s">
         <v>42</v>
@@ -19010,7 +19010,7 @@
         <v>88</v>
       </c>
       <c r="U52" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="V52" t="s">
         <v>264</v>
@@ -19060,19 +19060,19 @@
         <v>123456789012</v>
       </c>
       <c r="D53" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E53" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F53" t="s">
+        <v>523</v>
+      </c>
+      <c r="G53" t="s">
         <v>524</v>
       </c>
-      <c r="G53" t="s">
-        <v>525</v>
-      </c>
       <c r="I53" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="J53" t="s">
         <v>42</v>
@@ -19102,7 +19102,7 @@
         <v>88</v>
       </c>
       <c r="U53" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="V53" t="s">
         <v>266</v>
@@ -19152,19 +19152,19 @@
         <v>123456789012</v>
       </c>
       <c r="D54" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E54" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F54" t="s">
+        <v>523</v>
+      </c>
+      <c r="G54" t="s">
         <v>524</v>
       </c>
-      <c r="G54" t="s">
-        <v>525</v>
-      </c>
       <c r="I54" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="J54" t="s">
         <v>42</v>
@@ -19194,7 +19194,7 @@
         <v>88</v>
       </c>
       <c r="U54" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="V54" t="s">
         <v>268</v>
@@ -19244,19 +19244,19 @@
         <v>123456789012</v>
       </c>
       <c r="D55" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E55" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F55" t="s">
+        <v>523</v>
+      </c>
+      <c r="G55" t="s">
         <v>524</v>
       </c>
-      <c r="G55" t="s">
-        <v>525</v>
-      </c>
       <c r="I55" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="J55" t="s">
         <v>42</v>
@@ -19286,7 +19286,7 @@
         <v>88</v>
       </c>
       <c r="U55" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="V55" t="s">
         <v>270</v>
@@ -19336,19 +19336,19 @@
         <v>123456789012</v>
       </c>
       <c r="D56" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E56" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F56" t="s">
+        <v>523</v>
+      </c>
+      <c r="G56" t="s">
         <v>524</v>
       </c>
-      <c r="G56" t="s">
-        <v>525</v>
-      </c>
       <c r="I56" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="J56" t="s">
         <v>42</v>
@@ -19378,7 +19378,7 @@
         <v>88</v>
       </c>
       <c r="U56" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="V56" t="s">
         <v>272</v>
@@ -19428,19 +19428,19 @@
         <v>123456789012</v>
       </c>
       <c r="D57" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E57" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F57" t="s">
+        <v>523</v>
+      </c>
+      <c r="G57" t="s">
         <v>524</v>
       </c>
-      <c r="G57" t="s">
-        <v>525</v>
-      </c>
       <c r="I57" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="J57" t="s">
         <v>42</v>
@@ -19470,7 +19470,7 @@
         <v>88</v>
       </c>
       <c r="U57" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="V57" t="s">
         <v>274</v>
@@ -19520,19 +19520,19 @@
         <v>123456789012</v>
       </c>
       <c r="D58" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E58" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F58" t="s">
+        <v>523</v>
+      </c>
+      <c r="G58" t="s">
         <v>524</v>
       </c>
-      <c r="G58" t="s">
-        <v>525</v>
-      </c>
       <c r="I58" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="J58" t="s">
         <v>42</v>
@@ -19562,7 +19562,7 @@
         <v>88</v>
       </c>
       <c r="U58" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="V58" t="s">
         <v>276</v>
@@ -19612,19 +19612,19 @@
         <v>123456789012</v>
       </c>
       <c r="D59" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E59" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F59" t="s">
+        <v>523</v>
+      </c>
+      <c r="G59" t="s">
         <v>524</v>
       </c>
-      <c r="G59" t="s">
-        <v>525</v>
-      </c>
       <c r="I59" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="J59" t="s">
         <v>42</v>
@@ -19654,7 +19654,7 @@
         <v>88</v>
       </c>
       <c r="U59" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="V59" t="s">
         <v>278</v>
@@ -19704,19 +19704,19 @@
         <v>123456789012</v>
       </c>
       <c r="D60" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E60" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F60" t="s">
+        <v>523</v>
+      </c>
+      <c r="G60" t="s">
         <v>524</v>
       </c>
-      <c r="G60" t="s">
-        <v>525</v>
-      </c>
       <c r="I60" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="J60" t="s">
         <v>42</v>
@@ -19746,7 +19746,7 @@
         <v>88</v>
       </c>
       <c r="U60" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="V60" t="s">
         <v>280</v>
@@ -19799,19 +19799,19 @@
         <v>123456789012</v>
       </c>
       <c r="D61" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E61" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F61" t="s">
+        <v>523</v>
+      </c>
+      <c r="G61" t="s">
         <v>524</v>
       </c>
-      <c r="G61" t="s">
-        <v>525</v>
-      </c>
       <c r="I61" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="J61" t="s">
         <v>42</v>
@@ -19841,7 +19841,7 @@
         <v>88</v>
       </c>
       <c r="U61" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="V61" t="s">
         <v>232</v>
@@ -19891,19 +19891,19 @@
         <v>123456789012</v>
       </c>
       <c r="D62" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E62" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F62" t="s">
+        <v>523</v>
+      </c>
+      <c r="G62" t="s">
         <v>524</v>
       </c>
-      <c r="G62" t="s">
-        <v>525</v>
-      </c>
       <c r="I62" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="J62" t="s">
         <v>42</v>
@@ -19933,7 +19933,7 @@
         <v>88</v>
       </c>
       <c r="U62" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="V62" t="s">
         <v>283</v>
@@ -19983,19 +19983,19 @@
         <v>123456789012</v>
       </c>
       <c r="D63" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E63" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F63" t="s">
+        <v>523</v>
+      </c>
+      <c r="G63" t="s">
         <v>524</v>
       </c>
-      <c r="G63" t="s">
-        <v>525</v>
-      </c>
       <c r="I63" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="J63" t="s">
         <v>42</v>
@@ -20025,7 +20025,7 @@
         <v>88</v>
       </c>
       <c r="U63" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="V63" t="s">
         <v>285</v>
@@ -20075,19 +20075,19 @@
         <v>123456789012</v>
       </c>
       <c r="D64" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E64" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F64" t="s">
+        <v>523</v>
+      </c>
+      <c r="G64" t="s">
         <v>524</v>
       </c>
-      <c r="G64" t="s">
-        <v>525</v>
-      </c>
       <c r="I64" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J64" t="s">
         <v>42</v>
@@ -20117,7 +20117,7 @@
         <v>88</v>
       </c>
       <c r="U64" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="V64" t="s">
         <v>287</v>
@@ -20167,19 +20167,19 @@
         <v>123456789012</v>
       </c>
       <c r="D65" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E65" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F65" t="s">
+        <v>523</v>
+      </c>
+      <c r="G65" t="s">
         <v>524</v>
       </c>
-      <c r="G65" t="s">
-        <v>525</v>
-      </c>
       <c r="I65" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="J65" t="s">
         <v>42</v>
@@ -20209,7 +20209,7 @@
         <v>88</v>
       </c>
       <c r="U65" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="V65" t="s">
         <v>289</v>
@@ -20259,19 +20259,19 @@
         <v>123456789012</v>
       </c>
       <c r="D66" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E66" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F66" t="s">
+        <v>523</v>
+      </c>
+      <c r="G66" t="s">
         <v>524</v>
       </c>
-      <c r="G66" t="s">
-        <v>525</v>
-      </c>
       <c r="I66" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="J66" t="s">
         <v>42</v>
@@ -20301,7 +20301,7 @@
         <v>88</v>
       </c>
       <c r="U66" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="V66" t="s">
         <v>291</v>
@@ -20354,19 +20354,19 @@
         <v>123456789012</v>
       </c>
       <c r="D67" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E67" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F67" t="s">
+        <v>523</v>
+      </c>
+      <c r="G67" t="s">
         <v>524</v>
       </c>
-      <c r="G67" t="s">
-        <v>525</v>
-      </c>
       <c r="I67" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="J67" t="s">
         <v>42</v>
@@ -20396,7 +20396,7 @@
         <v>88</v>
       </c>
       <c r="U67" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="V67" t="s">
         <v>234</v>
@@ -20446,19 +20446,19 @@
         <v>123456789012</v>
       </c>
       <c r="D68" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E68" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F68" t="s">
+        <v>523</v>
+      </c>
+      <c r="G68" t="s">
         <v>524</v>
       </c>
-      <c r="G68" t="s">
-        <v>525</v>
-      </c>
       <c r="I68" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="J68" t="s">
         <v>42</v>
@@ -20488,7 +20488,7 @@
         <v>88</v>
       </c>
       <c r="U68" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="V68" t="s">
         <v>294</v>
@@ -20538,19 +20538,19 @@
         <v>123456789012</v>
       </c>
       <c r="D69" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E69" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F69" t="s">
+        <v>523</v>
+      </c>
+      <c r="G69" t="s">
         <v>524</v>
       </c>
-      <c r="G69" t="s">
-        <v>525</v>
-      </c>
       <c r="I69" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="J69" t="s">
         <v>42</v>
@@ -20580,7 +20580,7 @@
         <v>88</v>
       </c>
       <c r="U69" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="V69" t="s">
         <v>296</v>
@@ -20630,19 +20630,19 @@
         <v>123456789012</v>
       </c>
       <c r="D70" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E70" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F70" t="s">
+        <v>523</v>
+      </c>
+      <c r="G70" t="s">
         <v>524</v>
       </c>
-      <c r="G70" t="s">
-        <v>525</v>
-      </c>
       <c r="I70" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="J70" t="s">
         <v>42</v>
@@ -20672,7 +20672,7 @@
         <v>88</v>
       </c>
       <c r="U70" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="V70" t="s">
         <v>298</v>
@@ -20722,19 +20722,19 @@
         <v>123456789012</v>
       </c>
       <c r="D71" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E71" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F71" t="s">
+        <v>523</v>
+      </c>
+      <c r="G71" t="s">
         <v>524</v>
       </c>
-      <c r="G71" t="s">
-        <v>525</v>
-      </c>
       <c r="I71" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="J71" t="s">
         <v>42</v>
@@ -20767,7 +20767,7 @@
         <v>104</v>
       </c>
       <c r="U71" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="V71" t="s">
         <v>300</v>
@@ -20811,19 +20811,19 @@
         <v>123456789012</v>
       </c>
       <c r="D72" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E72" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F72" t="s">
+        <v>523</v>
+      </c>
+      <c r="G72" t="s">
         <v>524</v>
       </c>
-      <c r="G72" t="s">
-        <v>525</v>
-      </c>
       <c r="I72" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="J72" t="s">
         <v>42</v>
@@ -20856,7 +20856,7 @@
         <v>104</v>
       </c>
       <c r="U72" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="V72" t="s">
         <v>300</v>
@@ -20906,19 +20906,19 @@
         <v>123456789012</v>
       </c>
       <c r="D73" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E73" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F73" t="s">
+        <v>523</v>
+      </c>
+      <c r="G73" t="s">
         <v>524</v>
       </c>
-      <c r="G73" t="s">
-        <v>525</v>
-      </c>
       <c r="I73" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="J73" t="s">
         <v>42</v>
@@ -20951,7 +20951,7 @@
         <v>121</v>
       </c>
       <c r="U73" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="V73">
         <v>123456789012</v>
@@ -20995,19 +20995,19 @@
         <v>123456789012</v>
       </c>
       <c r="D74" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E74" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F74" t="s">
+        <v>523</v>
+      </c>
+      <c r="G74" t="s">
         <v>524</v>
       </c>
-      <c r="G74" t="s">
-        <v>525</v>
-      </c>
       <c r="I74" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="J74" t="s">
         <v>42</v>
@@ -21040,7 +21040,7 @@
         <v>121</v>
       </c>
       <c r="U74" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="V74">
         <v>123456789012</v>
@@ -21087,19 +21087,19 @@
         <v>123456789012</v>
       </c>
       <c r="D75" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E75" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F75" t="s">
+        <v>523</v>
+      </c>
+      <c r="G75" t="s">
         <v>524</v>
       </c>
-      <c r="G75" t="s">
-        <v>525</v>
-      </c>
       <c r="I75" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="J75" t="s">
         <v>42</v>
@@ -21132,7 +21132,7 @@
         <v>133</v>
       </c>
       <c r="U75" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="V75" t="s">
         <v>308</v>
@@ -21176,19 +21176,19 @@
         <v>123456789012</v>
       </c>
       <c r="D76" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E76" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F76" t="s">
+        <v>523</v>
+      </c>
+      <c r="G76" t="s">
         <v>524</v>
       </c>
-      <c r="G76" t="s">
-        <v>525</v>
-      </c>
       <c r="I76" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="J76" t="s">
         <v>42</v>
@@ -21224,7 +21224,7 @@
         <v>142</v>
       </c>
       <c r="U76" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="V76" t="s">
         <v>310</v>
@@ -21277,19 +21277,19 @@
         <v>123456789012</v>
       </c>
       <c r="D77" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E77" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F77" t="s">
+        <v>523</v>
+      </c>
+      <c r="G77" t="s">
         <v>524</v>
       </c>
-      <c r="G77" t="s">
-        <v>525</v>
-      </c>
       <c r="I77" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="J77" t="s">
         <v>42</v>
@@ -21325,7 +21325,7 @@
         <v>142</v>
       </c>
       <c r="U77" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="V77" t="s">
         <v>313</v>
@@ -21378,19 +21378,19 @@
         <v>123456789012</v>
       </c>
       <c r="D78" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E78" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F78" t="s">
+        <v>523</v>
+      </c>
+      <c r="G78" t="s">
         <v>524</v>
       </c>
-      <c r="G78" t="s">
-        <v>525</v>
-      </c>
       <c r="I78" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="J78" t="s">
         <v>42</v>
@@ -21426,7 +21426,7 @@
         <v>142</v>
       </c>
       <c r="U78" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="V78" t="s">
         <v>315</v>
@@ -21479,19 +21479,19 @@
         <v>123456789012</v>
       </c>
       <c r="D79" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E79" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F79" t="s">
+        <v>523</v>
+      </c>
+      <c r="G79" t="s">
         <v>524</v>
       </c>
-      <c r="G79" t="s">
-        <v>525</v>
-      </c>
       <c r="I79" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="J79" t="s">
         <v>42</v>
@@ -21527,7 +21527,7 @@
         <v>142</v>
       </c>
       <c r="U79" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="V79" t="s">
         <v>317</v>
@@ -21580,19 +21580,19 @@
         <v>123456789012</v>
       </c>
       <c r="D80" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E80" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F80" t="s">
+        <v>523</v>
+      </c>
+      <c r="G80" t="s">
         <v>524</v>
       </c>
-      <c r="G80" t="s">
-        <v>525</v>
-      </c>
       <c r="I80" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="J80" t="s">
         <v>42</v>
@@ -21628,13 +21628,13 @@
         <v>142</v>
       </c>
       <c r="U80" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="V80" t="s">
         <v>319</v>
       </c>
       <c r="X80" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="Y80" t="s">
         <v>42</v>
@@ -21684,19 +21684,19 @@
         <v>123456789012</v>
       </c>
       <c r="D81" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E81" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F81" t="s">
+        <v>523</v>
+      </c>
+      <c r="G81" t="s">
         <v>524</v>
       </c>
-      <c r="G81" t="s">
-        <v>525</v>
-      </c>
       <c r="I81" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="J81" t="s">
         <v>42</v>
@@ -21732,13 +21732,13 @@
         <v>142</v>
       </c>
       <c r="U81" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="V81" t="s">
         <v>321</v>
       </c>
       <c r="X81" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="Y81" t="s">
         <v>42</v>
@@ -21788,19 +21788,19 @@
         <v>123456789012</v>
       </c>
       <c r="D82" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E82" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F82" t="s">
+        <v>523</v>
+      </c>
+      <c r="G82" t="s">
         <v>524</v>
       </c>
-      <c r="G82" t="s">
-        <v>525</v>
-      </c>
       <c r="I82" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="J82" t="s">
         <v>42</v>
@@ -21836,13 +21836,13 @@
         <v>142</v>
       </c>
       <c r="U82" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="V82" t="s">
         <v>323</v>
       </c>
       <c r="X82" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="Y82" t="s">
         <v>42</v>
@@ -21892,19 +21892,19 @@
         <v>123456789012</v>
       </c>
       <c r="D83" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E83" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F83" t="s">
+        <v>523</v>
+      </c>
+      <c r="G83" t="s">
         <v>524</v>
       </c>
-      <c r="G83" t="s">
-        <v>525</v>
-      </c>
       <c r="I83" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="J83" t="s">
         <v>42</v>
@@ -21940,13 +21940,13 @@
         <v>142</v>
       </c>
       <c r="U83" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="V83" t="s">
         <v>325</v>
       </c>
       <c r="X83" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="Y83" t="s">
         <v>42</v>
@@ -21996,19 +21996,19 @@
         <v>123456789012</v>
       </c>
       <c r="D84" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E84" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F84" t="s">
+        <v>523</v>
+      </c>
+      <c r="G84" t="s">
         <v>524</v>
       </c>
-      <c r="G84" t="s">
-        <v>525</v>
-      </c>
       <c r="I84" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="J84" t="s">
         <v>42</v>
@@ -22044,7 +22044,7 @@
         <v>142</v>
       </c>
       <c r="U84" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="V84" t="s">
         <v>327</v>
@@ -22097,19 +22097,19 @@
         <v>123456789012</v>
       </c>
       <c r="D85" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E85" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F85" t="s">
+        <v>523</v>
+      </c>
+      <c r="G85" t="s">
         <v>524</v>
       </c>
-      <c r="G85" t="s">
-        <v>525</v>
-      </c>
       <c r="I85" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="J85" t="s">
         <v>42</v>
@@ -22145,7 +22145,7 @@
         <v>142</v>
       </c>
       <c r="U85" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="V85" t="s">
         <v>310</v>
@@ -22198,19 +22198,19 @@
         <v>123456789012</v>
       </c>
       <c r="D86" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E86" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F86" t="s">
+        <v>523</v>
+      </c>
+      <c r="G86" t="s">
         <v>524</v>
       </c>
-      <c r="G86" t="s">
-        <v>525</v>
-      </c>
       <c r="I86" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="J86" t="s">
         <v>42</v>
@@ -22246,7 +22246,7 @@
         <v>142</v>
       </c>
       <c r="U86" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="V86" t="s">
         <v>313</v>
@@ -22299,19 +22299,19 @@
         <v>123456789012</v>
       </c>
       <c r="D87" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E87" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F87" t="s">
+        <v>523</v>
+      </c>
+      <c r="G87" t="s">
         <v>524</v>
       </c>
-      <c r="G87" t="s">
-        <v>525</v>
-      </c>
       <c r="I87" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="J87" t="s">
         <v>42</v>
@@ -22347,7 +22347,7 @@
         <v>142</v>
       </c>
       <c r="U87" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="V87" t="s">
         <v>329</v>
@@ -22400,19 +22400,19 @@
         <v>123456789012</v>
       </c>
       <c r="D88" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E88" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F88" t="s">
+        <v>523</v>
+      </c>
+      <c r="G88" t="s">
         <v>524</v>
       </c>
-      <c r="G88" t="s">
-        <v>525</v>
-      </c>
       <c r="I88" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="J88" t="s">
         <v>42</v>
@@ -22448,7 +22448,7 @@
         <v>142</v>
       </c>
       <c r="U88" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="V88" t="s">
         <v>327</v>
@@ -22501,19 +22501,19 @@
         <v>123456789012</v>
       </c>
       <c r="D89" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E89" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F89" t="s">
+        <v>523</v>
+      </c>
+      <c r="G89" t="s">
         <v>524</v>
       </c>
-      <c r="G89" t="s">
-        <v>525</v>
-      </c>
       <c r="I89" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="J89" t="s">
         <v>42</v>
@@ -22549,7 +22549,7 @@
         <v>142</v>
       </c>
       <c r="U89" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="V89" t="s">
         <v>331</v>
@@ -22602,19 +22602,19 @@
         <v>123456789012</v>
       </c>
       <c r="D90" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E90" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F90" t="s">
+        <v>523</v>
+      </c>
+      <c r="G90" t="s">
         <v>524</v>
       </c>
-      <c r="G90" t="s">
-        <v>525</v>
-      </c>
       <c r="I90" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="J90" t="s">
         <v>42</v>
@@ -22650,7 +22650,7 @@
         <v>142</v>
       </c>
       <c r="U90" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="V90" t="s">
         <v>327</v>
@@ -22703,19 +22703,19 @@
         <v>123456789012</v>
       </c>
       <c r="D91" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E91" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F91" t="s">
+        <v>523</v>
+      </c>
+      <c r="G91" t="s">
         <v>524</v>
       </c>
-      <c r="G91" t="s">
-        <v>525</v>
-      </c>
       <c r="I91" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="J91" t="s">
         <v>42</v>
@@ -22748,7 +22748,7 @@
         <v>152</v>
       </c>
       <c r="U91" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="V91" t="s">
         <v>310</v>
@@ -22795,19 +22795,19 @@
         <v>123456789012</v>
       </c>
       <c r="D92" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E92" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F92" t="s">
+        <v>523</v>
+      </c>
+      <c r="G92" t="s">
         <v>524</v>
       </c>
-      <c r="G92" t="s">
-        <v>525</v>
-      </c>
       <c r="I92" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="J92" t="s">
         <v>42</v>
@@ -22840,7 +22840,7 @@
         <v>152</v>
       </c>
       <c r="U92" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="V92" t="s">
         <v>313</v>
@@ -22887,19 +22887,19 @@
         <v>123456789012</v>
       </c>
       <c r="D93" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E93" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F93" t="s">
+        <v>523</v>
+      </c>
+      <c r="G93" t="s">
         <v>524</v>
       </c>
-      <c r="G93" t="s">
-        <v>525</v>
-      </c>
       <c r="I93" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="J93" t="s">
         <v>42</v>
@@ -22932,7 +22932,7 @@
         <v>152</v>
       </c>
       <c r="U93" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="V93" t="s">
         <v>319</v>
@@ -22979,19 +22979,19 @@
         <v>123456789012</v>
       </c>
       <c r="D94" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E94" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F94" t="s">
+        <v>523</v>
+      </c>
+      <c r="G94" t="s">
         <v>524</v>
       </c>
-      <c r="G94" t="s">
-        <v>525</v>
-      </c>
       <c r="I94" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="J94" t="s">
         <v>42</v>
@@ -23024,7 +23024,7 @@
         <v>152</v>
       </c>
       <c r="U94" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="V94" t="s">
         <v>310</v>
@@ -23071,19 +23071,19 @@
         <v>123456789012</v>
       </c>
       <c r="D95" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E95" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F95" t="s">
+        <v>523</v>
+      </c>
+      <c r="G95" t="s">
         <v>524</v>
       </c>
-      <c r="G95" t="s">
-        <v>525</v>
-      </c>
       <c r="I95" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="J95" t="s">
         <v>42</v>
@@ -23116,7 +23116,7 @@
         <v>152</v>
       </c>
       <c r="U95" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="V95" t="s">
         <v>313</v>
@@ -23163,19 +23163,19 @@
         <v>123456789012</v>
       </c>
       <c r="D96" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E96" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F96" t="s">
+        <v>523</v>
+      </c>
+      <c r="G96" t="s">
         <v>524</v>
       </c>
-      <c r="G96" t="s">
-        <v>525</v>
-      </c>
       <c r="I96" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="J96" t="s">
         <v>42</v>
@@ -23208,7 +23208,7 @@
         <v>152</v>
       </c>
       <c r="U96" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="V96" t="s">
         <v>329</v>
@@ -23255,19 +23255,19 @@
         <v>123456789012</v>
       </c>
       <c r="D97" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E97" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F97" t="s">
+        <v>523</v>
+      </c>
+      <c r="G97" t="s">
         <v>524</v>
       </c>
-      <c r="G97" t="s">
-        <v>525</v>
-      </c>
       <c r="I97" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="J97" t="s">
         <v>42</v>
@@ -23300,7 +23300,7 @@
         <v>152</v>
       </c>
       <c r="U97" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="V97" t="s">
         <v>331</v>
@@ -23347,19 +23347,19 @@
         <v>123456789012</v>
       </c>
       <c r="D98" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E98" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F98" t="s">
+        <v>523</v>
+      </c>
+      <c r="G98" t="s">
         <v>524</v>
       </c>
-      <c r="G98" t="s">
-        <v>525</v>
-      </c>
       <c r="I98" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="J98" t="s">
         <v>42</v>
@@ -23395,7 +23395,7 @@
         <v>142</v>
       </c>
       <c r="U98" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="V98" t="s">
         <v>315</v>
@@ -23448,19 +23448,19 @@
         <v>123456789012</v>
       </c>
       <c r="D99" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E99" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F99" t="s">
+        <v>523</v>
+      </c>
+      <c r="G99" t="s">
         <v>524</v>
       </c>
-      <c r="G99" t="s">
-        <v>525</v>
-      </c>
       <c r="I99" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="J99" t="s">
         <v>42</v>
@@ -23496,7 +23496,7 @@
         <v>142</v>
       </c>
       <c r="U99" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="V99" t="s">
         <v>317</v>
@@ -23549,19 +23549,19 @@
         <v>123456789012</v>
       </c>
       <c r="D100" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E100" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F100" t="s">
+        <v>523</v>
+      </c>
+      <c r="G100" t="s">
         <v>524</v>
       </c>
-      <c r="G100" t="s">
-        <v>525</v>
-      </c>
       <c r="I100" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="J100" t="s">
         <v>42</v>
@@ -23597,13 +23597,13 @@
         <v>142</v>
       </c>
       <c r="U100" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="V100" t="s">
         <v>319</v>
       </c>
       <c r="X100" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="Y100" t="s">
         <v>42</v>
